--- a/Formatos/concentrado_municipal_plantilla.xlsx
+++ b/Formatos/concentrado_municipal_plantilla.xlsx
@@ -6784,10 +6784,10 @@
       <c r="X1" s="5"/>
       <c r="Y1" s="5"/>
       <c r="Z1" s="6"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
       <c r="AC1" s="6"/>
-      <c r="AD1" s="1"/>
+      <c r="AD1" s="5"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
